--- a/xlsx/系统/单位自动创建系统.xlsx
+++ b/xlsx/系统/单位自动创建系统.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19320" windowHeight="8870"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="单位自动创建系统.ts" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
     <t>dwzdcjxt001</t>
   </si>
   <si>
-    <t>hfoo</t>
+    <t>H004</t>
   </si>
   <si>
     <t>{x:100,y:0}</t>
@@ -1075,16 +1075,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="15.8090909090909" customWidth="1"/>
-    <col min="2" max="2" width="19.9818181818182" customWidth="1"/>
-    <col min="3" max="4" width="13.6818181818182" customWidth="1"/>
-    <col min="5" max="5" width="24.7636363636364" customWidth="1"/>
-    <col min="6" max="6" width="26.9545454545455" customWidth="1"/>
-    <col min="7" max="7" width="19.7909090909091" customWidth="1"/>
-    <col min="8" max="8" width="14.0181818181818" customWidth="1"/>
-    <col min="9" max="9" width="22.9727272727273" customWidth="1"/>
+    <col min="1" max="1" width="15.8083333333333" customWidth="1"/>
+    <col min="2" max="2" width="19.9833333333333" customWidth="1"/>
+    <col min="3" max="4" width="13.6833333333333" customWidth="1"/>
+    <col min="5" max="5" width="24.7666666666667" customWidth="1"/>
+    <col min="6" max="6" width="26.9583333333333" customWidth="1"/>
+    <col min="7" max="7" width="19.7916666666667" customWidth="1"/>
+    <col min="8" max="8" width="14.0166666666667" customWidth="1"/>
+    <col min="9" max="9" width="22.975" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="58" customHeight="1" spans="1:9">

--- a/xlsx/系统/单位自动创建系统.xlsx
+++ b/xlsx/系统/单位自动创建系统.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>id</t>
   </si>
@@ -86,15 +86,6 @@
   </si>
   <si>
     <t>reviveTime</t>
-  </si>
-  <si>
-    <t>dwzdcjxt001</t>
-  </si>
-  <si>
-    <t>H004</t>
-  </si>
-  <si>
-    <t>{x:100,y:0}</t>
   </si>
   <si>
     <t>dwzdcjxt002</t>
@@ -1074,8 +1065,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="15.8083333333333" customWidth="1"/>
     <col min="2" max="2" width="19.9833333333333" customWidth="1"/>
@@ -1145,7 +1136,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1165,29 +1156,6 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4">
-        <v>0.01</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
         <v>100</v>
       </c>
     </row>
